--- a/forms/trg/Formulir_TRG_flowliqtion.xlsx
+++ b/forms/trg/Formulir_TRG_flowliqtion.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B33)</f>
+        <f>COUNTA(Anggota!B5:B34)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F33)</f>
+        <f>COUNTA(Anggota!F5:F34)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,31 +913,35 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ariningsih Suprapti, ST, MT</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Dr. Eng. Ardy Arsyad, ST, M.Eng.Sc</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>Earthquake Geotechnical Engineering, Seismic Induced Liquefaction, Landslide Mitigation, and Artificial Inteligence for Geotechnical Engineering</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9513-6386</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>5990034</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>52163103400</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Erfan Syamsuddin, SSi, MT</t>
+          <t>Ariningsih Suprapti, ST, MT</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Geophysics measurements</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ariningsih Suprapti, ST, MT</t>
+          <t>Dr. Erfan Syamsuddin, SSi, MT</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +1006,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>Geophysics measurements</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1028,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Erfan Syamsuddin, SSi, MT</t>
+          <t>Ariningsih Suprapti, ST, MT</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1043,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Geophysics measurements</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,22 +1065,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Professor. Mitsu Okamura</t>
+          <t>Dr. Erfan Syamsuddin, SSi, MT</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Graduate School of Science and Engineering Ehime University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Soil Liquefaction, Liquefactuion Countermeasure, Aseismic Design,</t>
+          <t>Geophysics measurements</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,22 +1102,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Professor. Hemanta Hazarika</t>
+          <t>Professor. Mitsu Okamura</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Graaduate School of Engineering Kyushu University Japan</t>
+          <t>Graduate School of Science and Engineering Ehime University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Geotechnical Earthquake Engineering</t>
+          <t>Soil Liquefaction, Liquefactuion Countermeasure, Aseismic Design,</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,17 +1139,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kohei Ono</t>
+          <t>Professor. Hemanta Hazarika</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Ehime University</t>
+          <t>Graaduate School of Engineering Kyushu University Japan</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1172,22 +1176,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Masyhur Irsyam, MSE</t>
+          <t>Dr. Kohei Ono</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Bandung Institute of Technology (ITB)</t>
+          <t>Ehime University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Geotechnical Earthquake Engineering, Foundation Engineering, Soil Improvement</t>
+          <t>Geotechnical Earthquake Engineering</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,22 +1213,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mahdi Ibrahim Tanjung, ST, MT</t>
+          <t>Prof. Dr. Masyhur Irsyam, MSE</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Balai Hidrolika dan Geoteknik Keairan,Kementerian PU</t>
+          <t>Bandung Institute of Technology (ITB)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Geotechnics, Liquefaction, Soil Dynamics, Earthquake Engineering, Slope Stability</t>
+          <t>Geotechnical Earthquake Engineering, Foundation Engineering, Soil Improvement</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,22 +1250,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Arifin Beddu, ST, MT</t>
+          <t>Dr. Mahdi Ibrahim Tanjung, ST, MT</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Tadulako University Palu</t>
+          <t>Balai Hidrolika dan Geoteknik Keairan,Kementerian PU</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Geotechnics, Liquefaction</t>
+          <t>Geotechnics, Liquefaction, Soil Dynamics, Earthquake Engineering, Slope Stability</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1283,12 +1287,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Rustan Effendi, SSi, MT</t>
+          <t>Dr. Arifin Beddu, ST, MT</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1298,7 +1302,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Exploration of Geophysics</t>
+          <t>Geotechnics, Liquefaction</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1320,16 +1324,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Asyhari</t>
+          <t>Dr. Ir. Rustan Effendi, SSi, MT</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Tadulako University Palu</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Exploration of Geophysics</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1349,12 +1361,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Yunus</t>
+          <t>Muhammad Asyhari</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1378,24 +1390,16 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Febriansyah Darmawan</t>
+          <t>Muhammad Yunus</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Geoteknik</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1415,12 +1419,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Fidya Fattimiyah Azzahra</t>
+          <t>Muhammad Febriansyah Darmawan</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1452,12 +1456,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Deniel Edyson Makadanan</t>
+          <t>Fidya Fattimiyah Azzahra</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1467,7 +1471,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Geoteknik, Teknik Sipil</t>
+          <t>Geoteknik</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1489,22 +1493,22 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Widjojo Adi Prakoso, MSc, PhD</t>
+          <t>Deniel Edyson Makadanan</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>University of Indonesia (UI)</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Geotechnical Earthquake Engineering</t>
+          <t>Geoteknik, Teknik Sipil</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1524,10 +1528,26 @@
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="11" t="n"/>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Prof. Ir. Widjojo Adi Prakoso, MSc, PhD</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>University of Indonesia (UI)</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Geotechnical Earthquake Engineering</t>
+        </is>
+      </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
@@ -1535,7 +1555,11 @@
       <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1724,15 +1748,32 @@
       <c r="L33" s="12" t="n"/>
       <c r="M33" s="12" t="n"/>
     </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_flowliqtion.xlsx
+++ b/forms/trg/Formulir_TRG_flowliqtion.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Eng. Ardy Arsyad, ST, M.Eng.Sc</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
